--- a/data_extactor/batch_10_fa/trimmed/batch_0004_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0004_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | ایمنی و امنیت عمومی | روان‌شناسی | امور پرسنلی و منابع انسانی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | بیان شفاهی | استدلال قیاسی | درک شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان و مراقبان کودک | مدیران مدارس ابتدایی و متوسطه | آموزگاران مدارس ابتدایی، به‌استثنای آموزش استثنایی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مربیان پیش‌دبستانی، به‌استثنای آموزش استثنایی | مربیان آموزش مهدکودک و پیش‌دبستانی، به‌استثنای آموزش استثنایی | معلمان آموزش استثنایی مهدکودک و پیش‌دبستانی</t>
+          <t>مربیان و مراقبان کودک | مدیران آموزشی مقاطع ابتدایی و متوسطه | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره پیش‌دبستانی و آمادگی، به‌جز آموزش استثنایی | مربیان پیش‌دبستانی و مهدکودک، به‌جز آموزش استثنایی | معلمان آموزش استثنایی دوره آمادگی و نوآموزان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | راهبردهای یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>سخن گفتن | گوش دادن فعال | راهبردهای یادگیری | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | امور اداری | خدمات مشتریان و خدمات فردی | امور پرسنلی و منابع انسانی | روان‌شناسی | ایمنی و امنیت عمومی</t>
+          <t>آموزش و پرورش | مدیریت و اداره | اداری | خدمات مشتری و شخصی | پرسنل و منابع انسانی | روان‌شناسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران آموزش عالی | مشاوران تحصیلی، راهنمایی و شغلی | آموزگاران مدارس ابتدایی، به‌استثنای آموزش استثنایی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | دبیران دوره اول متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای | روان‌شناسان مدرسه | دبیران دوره دوم متوسطه، به‌استثنای آموزش استثنایی و فنی‌حرفه‌ای</t>
+          <t>مدیران آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | معلمان دوره اول متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای | روان‌شناسان مدارس | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | آموزش و تدریس | خدمات مشتریان و خدمات فردی | امور پرسنلی و منابع انسانی | امور اداری | ارتباطات و رسانه</t>
+          <t>مدیریت و اداره | آموزش و پرورش | خدمات مشتری و شخصی | پرسنل و منابع انسانی | اداری | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران مدارس ابتدایی و متوسطه | استادان علوم تربیتی دانشگاه | مشاوران تحصیلی، راهنمایی و شغلی | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | تحلیل‌گران مدیریت و بهبود فرایندها | دستیاران آموزشی و تدریس دانشگاه | مدیران آموزش و بهسازی منابع انسانی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مشاوران تحصیلی، شغلی و هدایت استعدادها | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارشناسان تحلیل مدیریت و روش‌ها | دستیاران آموزشی در آموزش عالی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | مدیریت و امور اداری | امور پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | روان‌شناسی | حقوق و امور دولتی | ارتباطات و رسانه</t>
+          <t>آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | روان‌شناسی | قانون و دولت | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران مدارس ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | هماهنگ‌کنندگان و برنامه‌ریزان آموزشی | مدیران آموزش و بهسازی منابع انسانی | کارشناسان آموزش و توسعه منابع انسانی | مشاوران تحصیلی، راهنمایی و شغلی</t>
+          <t>مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران آموزش عالی | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران آموزش و بهسازی | کارشناسان آموزش و توسعه منابع انسانی | مشاوران تحصیلی، شغلی و هدایت استعدادها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | ریاضیات | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | فنی و مهندسی | ریاضیات | مدیریت و امور اداری | مکانیک | کامپیوتر و الکترونیک | فیزیک</t>
+          <t>طراحی | مهندسی و فناوری | ریاضیات | مدیریت و اداره | مکانیک | رایانه و الکترونیک | فیزیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | تجسم فضایی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان عمران | مدیران پروژه‌های عمرانی و ساخت‌وساز | مهندسان برق | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | کارشناسان مدیریت پروژه</t>
+          <t>مهندسان عمران | مدیران پروژه‌های ساختمانی | مهندسان برق | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | شنیدن فعال | نظارت | یادگیری فعال | ریاضیات | علوم تجربی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>شیمی | فنی و مهندسی | ریاضیات | تولید و فراوری | کامپیوتر و الکترونیک | مکانیک | مدیریت و امور اداری</t>
+          <t>شیمی | مهندسی و فناوری | ریاضیات | تولید و فرآوری | رایانه و الکترونیک | مکانیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال استقرایی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های فراوری زیست‌سوخت | مدیران تولید زیست‌سوخت | مهندسان شیمی | مهندسان انرژی، به‌استثنای بادی و خورشیدی | مهندسان صنایع | مهندسان تولید و ساخت</t>
+          <t>مهندسان کشاورزی | تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | مهندسان شیمی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان صنایع | مهندسان تولید و ساخت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | صنایع غذایی و تولید خوراک | امور پرسنلی و منابع انسانی | فروش و بازاریابی | ریاضیات | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | تولید مواد غذایی | پرسنل و منابع انسانی | فروش و بازاریابی | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | توجه انتخابی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | توجه انتخابی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>سرآشپزان و آشپزان ارشد | آشپزان رستورانی | سرپرستان رده اول کارگران آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | میزبانان رستوران، سالن و کافه | گارسون‌ها و پیشخدمت‌های رستوران</t>
+          <t>سرآشپزان و آشپزان ارشد | آشپزان رستوران | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | کارگران آماده‌سازی غذا | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال | نگارش | درک مطلب | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ریاضیات | امور پرسنلی و منابع انسانی | امور اداری | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | ریاضیات | پرسنل و منابع انسانی | اداری | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خدمتگزاران و متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | سرپرستان رده اول کارکنان سالن‌های بازی و تفریحی | مدیران خدمات پذیرایی و غذا و نوشیدنی | مأموران مراقبت سالن و ناظران بازی‌ها | مدیران عمومی و عملیاتی | مدیران اقامتی و هتلداری</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | صندوق‌داران | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | مدیران خدمات پذیرایی و غذا و نوشیدنی | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مدیران کل و مدیران عملیات | مدیران هتل و مراکز اقامتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | ایمنی و امنیت عمومی | امور پرسنلی و منابع انسانی | امور اداری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | اداری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مربیان بدنسازی و ورزش‌های گروهی | سرپرستان رده اول ارائه‌دهندگان خدمات تفریحی و سرگرمی | مدیران عمومی و عملیاتی | مدیران اقامتی و هتلداری | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | کارکنان خدمات تفریحی و اوقات فراغت | راهنمایان تور و گردشگری</t>
+          <t>مربیان ورزش و آمادگی جسمانی گروهی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مدیران کل و مدیران عملیات | مدیران هتل و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | کارکنان و متصدیان امور تفریحی و اوقات فراغت | راهنمایان تور و گردشگری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مدیریت و امور اداری | امور پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | امور اداری | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | فروش و بازاریابی | اداری | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مسئولان خدمات اختصاصی هتل (کانسیرژ) | سرپرستان رده اول خدمات خانه‌داری و نظافت | سرپرستان رده اول ارائه‌دهندگان خدمات فردی | مدیران خدمات پذیرایی و غذا و نوشیدنی | متصدیان پذیرش هتل، متل و مراکز اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | مسئولان پذیرش و دفاتر اطلاعات</t>
+          <t>متصدیان تشریفات و خدمات میهمانان | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران خدمات پذیرایی و غذا و نوشیدنی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | متصدیان پذیرش و اطلاعات</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
